--- a/elenco_codici_studi.xlsx
+++ b/elenco_codici_studi.xlsx
@@ -23719,6 +23719,11 @@
           <t>T35P060</t>
         </is>
       </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2347">
       <c r="A2347" t="inlineStr">
@@ -23796,6 +23801,11 @@
           <t>T35P071</t>
         </is>
       </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2358">
       <c r="A2358" t="inlineStr">
@@ -23803,6 +23813,11 @@
           <t>T35P072</t>
         </is>
       </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2359">
       <c r="A2359" t="inlineStr">
@@ -23894,6 +23909,11 @@
           <t>T35P085</t>
         </is>
       </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2372">
       <c r="A2372" t="inlineStr">
@@ -23901,6 +23921,11 @@
           <t>T35P086</t>
         </is>
       </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2373">
       <c r="A2373" t="inlineStr">
@@ -23908,6 +23933,11 @@
           <t>T35P087</t>
         </is>
       </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2374">
       <c r="A2374" t="inlineStr">
@@ -23915,6 +23945,11 @@
           <t>T35P088</t>
         </is>
       </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2375">
       <c r="A2375" t="inlineStr">
@@ -23922,6 +23957,11 @@
           <t>T35P089</t>
         </is>
       </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2376">
       <c r="A2376" t="inlineStr">
@@ -23929,6 +23969,11 @@
           <t>T35P090</t>
         </is>
       </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2377">
       <c r="A2377" t="inlineStr">
@@ -23936,6 +23981,11 @@
           <t>T35P091</t>
         </is>
       </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2378">
       <c r="A2378" t="inlineStr">
@@ -23943,6 +23993,11 @@
           <t>T35P092</t>
         </is>
       </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2379">
       <c r="A2379" t="inlineStr">
@@ -23950,6 +24005,11 @@
           <t>T35P093</t>
         </is>
       </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2380">
       <c r="A2380" t="inlineStr">
@@ -23957,6 +24017,11 @@
           <t>T35P094</t>
         </is>
       </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2381">
       <c r="A2381" t="inlineStr">
@@ -23964,6 +24029,11 @@
           <t>T35P095</t>
         </is>
       </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2382">
       <c r="A2382" t="inlineStr">
@@ -23971,6 +24041,11 @@
           <t>T35P096</t>
         </is>
       </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2383">
       <c r="A2383" t="inlineStr">
@@ -23978,6 +24053,11 @@
           <t>T35P097</t>
         </is>
       </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
@@ -23985,6 +24065,11 @@
           <t>T35P098</t>
         </is>
       </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
@@ -23992,6 +24077,11 @@
           <t>T35P099</t>
         </is>
       </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2386">
       <c r="A2386" t="inlineStr">
@@ -23999,6 +24089,11 @@
           <t>T35P100</t>
         </is>
       </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2387">
       <c r="A2387" t="inlineStr">
@@ -24006,6 +24101,11 @@
           <t>T35P101</t>
         </is>
       </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2388">
       <c r="A2388" t="inlineStr">
@@ -24013,6 +24113,11 @@
           <t>T35P103</t>
         </is>
       </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2389">
       <c r="A2389" t="inlineStr">
@@ -24104,6 +24209,11 @@
           <t>T3AP013</t>
         </is>
       </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2402">
       <c r="A2402" t="inlineStr">
@@ -24111,6 +24221,11 @@
           <t>T3AP014</t>
         </is>
       </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2403">
       <c r="A2403" t="inlineStr">
@@ -24118,6 +24233,11 @@
           <t>T3AP015</t>
         </is>
       </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2404">
       <c r="A2404" t="inlineStr">
@@ -24125,6 +24245,11 @@
           <t>T3AP016</t>
         </is>
       </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2405">
       <c r="A2405" t="inlineStr">
@@ -24132,6 +24257,11 @@
           <t>T3AP017</t>
         </is>
       </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2406">
       <c r="A2406" t="inlineStr">
@@ -24139,6 +24269,11 @@
           <t>T3AP018</t>
         </is>
       </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2407">
       <c r="A2407" t="inlineStr">
@@ -24195,6 +24330,11 @@
           <t>T3D3012</t>
         </is>
       </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2415">
       <c r="A2415" t="inlineStr">
@@ -24209,6 +24349,11 @@
           <t>T3K2001</t>
         </is>
       </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2417">
       <c r="A2417" t="inlineStr">
@@ -24398,6 +24543,11 @@
           <t>T3K2039</t>
         </is>
       </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2444">
       <c r="A2444" t="inlineStr">
@@ -24405,6 +24555,11 @@
           <t>T3K2041</t>
         </is>
       </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2445">
       <c r="A2445" t="inlineStr">
@@ -24412,6 +24567,11 @@
           <t>T3K2042</t>
         </is>
       </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2446">
       <c r="A2446" t="inlineStr">
@@ -24419,6 +24579,11 @@
           <t>T3K2043</t>
         </is>
       </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2447">
       <c r="A2447" t="inlineStr">
@@ -24426,6 +24591,11 @@
           <t>T3K2044</t>
         </is>
       </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2448">
       <c r="A2448" t="inlineStr">
@@ -24433,6 +24603,11 @@
           <t>T3K2045</t>
         </is>
       </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2449">
       <c r="A2449" t="inlineStr">
@@ -24440,6 +24615,11 @@
           <t>T3K2046</t>
         </is>
       </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2450">
       <c r="A2450" t="inlineStr">
@@ -24447,6 +24627,11 @@
           <t>T3K2047</t>
         </is>
       </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2451">
       <c r="A2451" t="inlineStr">
@@ -24454,6 +24639,11 @@
           <t>T3K2048</t>
         </is>
       </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2452">
       <c r="A2452" t="inlineStr">
@@ -24461,6 +24651,11 @@
           <t>T3K2049</t>
         </is>
       </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2453">
       <c r="A2453" t="inlineStr">
@@ -24468,6 +24663,11 @@
           <t>T3K2050</t>
         </is>
       </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2454">
       <c r="A2454" t="inlineStr">
@@ -24475,6 +24675,11 @@
           <t>T3K2051</t>
         </is>
       </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2455">
       <c r="A2455" t="inlineStr">
@@ -24482,6 +24687,11 @@
           <t>T3K2052</t>
         </is>
       </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2456">
       <c r="A2456" t="inlineStr">
@@ -24489,6 +24699,11 @@
           <t>T3K2053</t>
         </is>
       </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2457">
       <c r="A2457" t="inlineStr">
@@ -24496,6 +24711,11 @@
           <t>T3K2054</t>
         </is>
       </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2458">
       <c r="A2458" t="inlineStr">
@@ -24503,6 +24723,11 @@
           <t>T3K2055</t>
         </is>
       </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2459">
       <c r="A2459" t="inlineStr">
@@ -24510,6 +24735,11 @@
           <t>T3K2056</t>
         </is>
       </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2460">
       <c r="A2460" t="inlineStr">
@@ -24517,6 +24747,11 @@
           <t>T3K2057</t>
         </is>
       </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2461">
       <c r="A2461" t="inlineStr">
@@ -24524,6 +24759,11 @@
           <t>T3K2058</t>
         </is>
       </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2462">
       <c r="A2462" t="inlineStr">
@@ -24531,6 +24771,11 @@
           <t>T3K2059</t>
         </is>
       </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2463">
       <c r="A2463" t="inlineStr">
@@ -24538,6 +24783,11 @@
           <t>T3K2060</t>
         </is>
       </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2464">
       <c r="A2464" t="inlineStr">
@@ -24545,6 +24795,11 @@
           <t>T3K2061</t>
         </is>
       </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2465">
       <c r="A2465" t="inlineStr">
@@ -24552,6 +24807,11 @@
           <t>T3K2062</t>
         </is>
       </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2466">
       <c r="A2466" t="inlineStr">
@@ -24559,6 +24819,11 @@
           <t>T3K2063</t>
         </is>
       </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2467">
       <c r="A2467" t="inlineStr">
@@ -24566,6 +24831,11 @@
           <t>T3K2064</t>
         </is>
       </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2468">
       <c r="A2468" t="inlineStr">
@@ -24573,6 +24843,11 @@
           <t>T3K2065</t>
         </is>
       </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2469">
       <c r="A2469" t="inlineStr">
@@ -24587,6 +24862,11 @@
           <t>T40P002</t>
         </is>
       </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2471">
       <c r="A2471" t="inlineStr">
@@ -24594,6 +24874,11 @@
           <t>T40P003</t>
         </is>
       </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2472">
       <c r="A2472" t="inlineStr">
@@ -24601,6 +24886,11 @@
           <t>T40P005</t>
         </is>
       </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2473">
       <c r="A2473" t="inlineStr">
@@ -24608,6 +24898,11 @@
           <t>T40P009</t>
         </is>
       </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2474">
       <c r="A2474" t="inlineStr">
@@ -24615,6 +24910,11 @@
           <t>T40P010</t>
         </is>
       </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2475">
       <c r="A2475" t="inlineStr">
@@ -24643,6 +24943,11 @@
           <t>T40P015</t>
         </is>
       </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2479">
       <c r="A2479" t="inlineStr">
@@ -24664,6 +24969,11 @@
           <t>T40P019</t>
         </is>
       </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2482">
       <c r="A2482" t="inlineStr">
@@ -24671,6 +24981,11 @@
           <t>T450001</t>
         </is>
       </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2483">
       <c r="A2483" t="inlineStr">
@@ -24678,6 +24993,11 @@
           <t>T450002</t>
         </is>
       </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2484">
       <c r="A2484" t="inlineStr">
@@ -24685,6 +25005,11 @@
           <t>T450003</t>
         </is>
       </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2485">
       <c r="A2485" t="inlineStr">
@@ -24692,6 +25017,11 @@
           <t>T450004</t>
         </is>
       </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2486">
       <c r="A2486" t="inlineStr">
@@ -24748,6 +25078,11 @@
           <t>T90P007</t>
         </is>
       </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2494">
       <c r="A2494" t="inlineStr">
@@ -24755,6 +25090,11 @@
           <t>T90P008</t>
         </is>
       </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2495">
       <c r="A2495" t="inlineStr">
@@ -24762,6 +25102,11 @@
           <t>T90P009</t>
         </is>
       </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2496">
       <c r="A2496" t="inlineStr">
@@ -24769,6 +25114,11 @@
           <t>T90P010</t>
         </is>
       </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2497">
       <c r="A2497" t="inlineStr">
@@ -24776,6 +25126,11 @@
           <t>TGLO003</t>
         </is>
       </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2498">
       <c r="A2498" t="inlineStr">
@@ -24783,6 +25138,11 @@
           <t>TGLO004</t>
         </is>
       </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2499">
       <c r="A2499" t="inlineStr">
@@ -24790,6 +25150,11 @@
           <t>TGLO005</t>
         </is>
       </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2500">
       <c r="A2500" t="inlineStr">
@@ -24797,6 +25162,11 @@
           <t>TMXE001</t>
         </is>
       </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2501">
       <c r="A2501" t="inlineStr">
@@ -24804,6 +25174,11 @@
           <t>TMXE002</t>
         </is>
       </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2502">
       <c r="A2502" t="inlineStr">
@@ -24818,6 +25193,11 @@
           <t>TMXE037</t>
         </is>
       </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2504">
       <c r="A2504" t="inlineStr">
@@ -24860,6 +25240,11 @@
           <t>TMXE044</t>
         </is>
       </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2510">
       <c r="A2510" t="inlineStr">
@@ -24867,6 +25252,11 @@
           <t>TMXE045</t>
         </is>
       </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2511">
       <c r="A2511" t="inlineStr">
@@ -24874,6 +25264,11 @@
           <t>TMXE046</t>
         </is>
       </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2512">
       <c r="A2512" t="inlineStr">
@@ -24881,6 +25276,11 @@
           <t>TMXE047</t>
         </is>
       </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2513">
       <c r="A2513" t="inlineStr">
@@ -24888,6 +25288,11 @@
           <t>TNDM002</t>
         </is>
       </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2514">
       <c r="A2514" t="inlineStr">
@@ -24895,6 +25300,11 @@
           <t>TRT1001</t>
         </is>
       </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2515">
       <c r="A2515" t="inlineStr">
@@ -24902,6 +25312,11 @@
           <t>TRT1002</t>
         </is>
       </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2516">
       <c r="A2516" t="inlineStr">
@@ -24909,6 +25324,11 @@
           <t>TRT1003</t>
         </is>
       </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2517">
       <c r="A2517" t="inlineStr">
@@ -24916,6 +25336,11 @@
           <t>TRT1004</t>
         </is>
       </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2518">
       <c r="A2518" t="inlineStr">
@@ -24923,6 +25348,11 @@
           <t>TRT1005</t>
         </is>
       </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2519">
       <c r="A2519" t="inlineStr">
@@ -24930,6 +25360,11 @@
           <t>TRT1006</t>
         </is>
       </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2520">
       <c r="A2520" t="inlineStr">
@@ -24937,6 +25372,11 @@
           <t>TS10001</t>
         </is>
       </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2521">
       <c r="A2521" t="inlineStr">
@@ -24951,6 +25391,11 @@
           <t>TS10004</t>
         </is>
       </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2523">
       <c r="A2523" t="inlineStr">
@@ -24958,6 +25403,11 @@
           <t>TS10005</t>
         </is>
       </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2524">
       <c r="A2524" t="inlineStr">
@@ -24965,6 +25415,11 @@
           <t>TS10006</t>
         </is>
       </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2525">
       <c r="A2525" t="inlineStr">
@@ -24972,6 +25427,11 @@
           <t>TS10008</t>
         </is>
       </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2526">
       <c r="A2526" t="inlineStr">
@@ -24979,6 +25439,11 @@
           <t>TS10009</t>
         </is>
       </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2527">
       <c r="A2527" t="inlineStr">
@@ -24986,6 +25451,11 @@
           <t>TS10010</t>
         </is>
       </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2528">
       <c r="A2528" t="inlineStr">
@@ -24993,6 +25463,11 @@
           <t>TS10011</t>
         </is>
       </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2529">
       <c r="A2529" t="inlineStr">
@@ -25000,6 +25475,11 @@
           <t>TT10002</t>
         </is>
       </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2530">
       <c r="A2530" t="inlineStr">
@@ -25007,6 +25487,11 @@
           <t>TT30001</t>
         </is>
       </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2531">
       <c r="A2531" t="inlineStr">
@@ -25014,6 +25499,11 @@
           <t>TT30002</t>
         </is>
       </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2532">
       <c r="A2532" t="inlineStr">
@@ -25021,6 +25511,11 @@
           <t>TT30003</t>
         </is>
       </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2533">
       <c r="A2533" t="inlineStr">
@@ -25028,6 +25523,11 @@
           <t>TT30004</t>
         </is>
       </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2534">
       <c r="A2534" t="inlineStr">
@@ -25035,6 +25535,11 @@
           <t>TT30005</t>
         </is>
       </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2535">
       <c r="A2535" t="inlineStr">
@@ -25042,6 +25547,11 @@
           <t>TT30006</t>
         </is>
       </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2536">
       <c r="A2536" t="inlineStr">
@@ -25049,6 +25559,11 @@
           <t>TT30007</t>
         </is>
       </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2537">
       <c r="A2537" t="inlineStr">
@@ -25056,6 +25571,11 @@
           <t>TT30008</t>
         </is>
       </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2538">
       <c r="A2538" t="inlineStr">
@@ -25070,6 +25590,11 @@
           <t>TUNI002</t>
         </is>
       </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2540">
       <c r="A2540" t="inlineStr">
@@ -25077,6 +25602,11 @@
           <t>TUNI003</t>
         </is>
       </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2541">
       <c r="A2541" t="inlineStr">
@@ -25140,6 +25670,11 @@
           <t>TUNI015</t>
         </is>
       </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2550">
       <c r="A2550" t="inlineStr">
@@ -25147,6 +25682,11 @@
           <t>TUNI016</t>
         </is>
       </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2551">
       <c r="A2551" t="inlineStr">
@@ -25168,6 +25708,11 @@
           <t>TUNI019</t>
         </is>
       </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2554">
       <c r="A2554" t="inlineStr">
@@ -25189,6 +25734,11 @@
           <t>TUNI022</t>
         </is>
       </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2557">
       <c r="A2557" t="inlineStr">
@@ -25203,6 +25753,11 @@
           <t>TUNI026</t>
         </is>
       </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2559">
       <c r="A2559" t="inlineStr">
@@ -25231,6 +25786,11 @@
           <t>TUNI031</t>
         </is>
       </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2563">
       <c r="A2563" t="inlineStr">
@@ -25238,6 +25798,11 @@
           <t>TUNI032</t>
         </is>
       </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2564">
       <c r="A2564" t="inlineStr">
@@ -25245,6 +25810,11 @@
           <t>TUNI033</t>
         </is>
       </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2565">
       <c r="A2565" t="inlineStr">
@@ -25252,6 +25822,11 @@
           <t>TUNI034</t>
         </is>
       </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2566">
       <c r="A2566" t="inlineStr">
@@ -25259,6 +25834,11 @@
           <t>TUNI035</t>
         </is>
       </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2567">
       <c r="A2567" t="inlineStr">
@@ -25266,6 +25846,11 @@
           <t>TUNI036</t>
         </is>
       </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2568">
       <c r="A2568" t="inlineStr">
@@ -25273,6 +25858,11 @@
           <t>TUNI037</t>
         </is>
       </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2569">
       <c r="A2569" t="inlineStr">
@@ -25280,6 +25870,11 @@
           <t>TUNI038</t>
         </is>
       </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2570">
       <c r="A2570" t="inlineStr">
@@ -25287,6 +25882,11 @@
           <t>TUNI039</t>
         </is>
       </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2571">
       <c r="A2571" t="inlineStr">
@@ -25294,6 +25894,11 @@
           <t>TUNI040</t>
         </is>
       </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2572">
       <c r="A2572" t="inlineStr">
@@ -25301,6 +25906,11 @@
           <t>TUNI041</t>
         </is>
       </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2573">
       <c r="A2573" t="inlineStr">
@@ -25308,6 +25918,11 @@
           <t>TUNI043</t>
         </is>
       </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2574">
       <c r="A2574" t="inlineStr">
@@ -25315,6 +25930,11 @@
           <t>TUNI045</t>
         </is>
       </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2575">
       <c r="A2575" t="inlineStr">
@@ -25322,6 +25942,11 @@
           <t>TUNI046</t>
         </is>
       </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2576">
       <c r="A2576" t="inlineStr">
@@ -25329,6 +25954,11 @@
           <t>TUNI047</t>
         </is>
       </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2577">
       <c r="A2577" t="inlineStr">
@@ -25336,6 +25966,11 @@
           <t>TUNI048</t>
         </is>
       </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2578">
       <c r="A2578" t="inlineStr">
@@ -25343,6 +25978,11 @@
           <t>TUNI053</t>
         </is>
       </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2579">
       <c r="A2579" t="inlineStr">
@@ -25350,6 +25990,11 @@
           <t>TUNI054</t>
         </is>
       </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2580">
       <c r="A2580" t="inlineStr">
@@ -25357,6 +26002,11 @@
           <t>TUNI055</t>
         </is>
       </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2581">
       <c r="A2581" t="inlineStr">
@@ -25364,6 +26014,11 @@
           <t>TUNI056</t>
         </is>
       </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2582">
       <c r="A2582" t="inlineStr">
@@ -25371,6 +26026,11 @@
           <t>TUNI059</t>
         </is>
       </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2583">
       <c r="A2583" t="inlineStr">
@@ -25378,6 +26038,11 @@
           <t>TUNI060</t>
         </is>
       </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2584">
       <c r="A2584" t="inlineStr">
@@ -25385,6 +26050,11 @@
           <t>TUNI062</t>
         </is>
       </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2585">
       <c r="A2585" t="inlineStr">
@@ -25425,6 +26095,11 @@
       <c r="A2590" t="inlineStr">
         <is>
           <t>ULHD001</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>scaricato</t>
         </is>
       </c>
     </row>

--- a/elenco_codici_studi.xlsx
+++ b/elenco_codici_studi.xlsx
@@ -441,6 +441,11 @@
           <t>ATSP001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1146,6 +1151,11 @@
           <t>FLEX006</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1153,6 +1163,11 @@
           <t>FLEX007</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1160,6 +1175,11 @@
           <t>FLEX008</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4626,6 +4646,11 @@
           <t>J146271</t>
         </is>
       </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4693,6 +4718,11 @@
           <t>J146279</t>
         </is>
       </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -5084,6 +5114,11 @@
           <t>J146312</t>
         </is>
       </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -5271,6 +5306,11 @@
           <t>J146330</t>
         </is>
       </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -5302,6 +5342,11 @@
           <t>J146333</t>
         </is>
       </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -5628,6 +5673,11 @@
           <t>J146364</t>
         </is>
       </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -5707,6 +5757,11 @@
           <t>J146371</t>
         </is>
       </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -5798,6 +5853,11 @@
           <t>J146379</t>
         </is>
       </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -5836,6 +5896,11 @@
           <t>J146383</t>
         </is>
       </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -5843,6 +5908,11 @@
           <t>J146384</t>
         </is>
       </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -6037,6 +6107,11 @@
           <t>J156001</t>
         </is>
       </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -6599,6 +6674,11 @@
           <t>J247002</t>
         </is>
       </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -6613,6 +6693,11 @@
           <t>J247004</t>
         </is>
       </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -6627,6 +6712,11 @@
           <t>J247006</t>
         </is>
       </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -6648,6 +6738,11 @@
           <t>J247009</t>
         </is>
       </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -6655,6 +6750,11 @@
           <t>J247010</t>
         </is>
       </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -6662,6 +6762,11 @@
           <t>J247011</t>
         </is>
       </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -6669,6 +6774,11 @@
           <t>J247012</t>
         </is>
       </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -6676,6 +6786,11 @@
           <t>J247013</t>
         </is>
       </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -6683,6 +6798,11 @@
           <t>J247014</t>
         </is>
       </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -6690,6 +6810,11 @@
           <t>J247015</t>
         </is>
       </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -6697,6 +6822,11 @@
           <t>J247016</t>
         </is>
       </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -6704,6 +6834,11 @@
           <t>J247017</t>
         </is>
       </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -6711,6 +6846,11 @@
           <t>J247018</t>
         </is>
       </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -6718,6 +6858,11 @@
           <t>J247019</t>
         </is>
       </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -6725,6 +6870,11 @@
           <t>J247020</t>
         </is>
       </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -6732,6 +6882,11 @@
           <t>J247021</t>
         </is>
       </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -6739,6 +6894,11 @@
           <t>J247022</t>
         </is>
       </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -6746,6 +6906,11 @@
           <t>J247023</t>
         </is>
       </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -6753,6 +6918,11 @@
           <t>J247024</t>
         </is>
       </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -6760,6 +6930,11 @@
           <t>J247025</t>
         </is>
       </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -6767,6 +6942,11 @@
           <t>J247026</t>
         </is>
       </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -7593,6 +7773,11 @@
           <t>J247118</t>
         </is>
       </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -7642,6 +7827,11 @@
           <t>J247125</t>
         </is>
       </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -7656,6 +7846,11 @@
           <t>J247127</t>
         </is>
       </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -7663,6 +7858,11 @@
           <t>J247128</t>
         </is>
       </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -7670,6 +7870,11 @@
           <t>J247129</t>
         </is>
       </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -7677,6 +7882,11 @@
           <t>J247130</t>
         </is>
       </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -7684,6 +7894,11 @@
           <t>J247131</t>
         </is>
       </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -7691,6 +7906,11 @@
           <t>J247132</t>
         </is>
       </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -7698,6 +7918,11 @@
           <t>J247133</t>
         </is>
       </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -7705,6 +7930,11 @@
           <t>J247134</t>
         </is>
       </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -7712,6 +7942,11 @@
           <t>J247135</t>
         </is>
       </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -7719,6 +7954,11 @@
           <t>J247136</t>
         </is>
       </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -7726,6 +7966,11 @@
           <t>J247137</t>
         </is>
       </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -9805,6 +10050,11 @@
           <t>J255236</t>
         </is>
       </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -10106,6 +10356,11 @@
           <t>J255279</t>
         </is>
       </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -10113,6 +10368,11 @@
           <t>J255280</t>
         </is>
       </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -10127,6 +10387,11 @@
           <t>J255282</t>
         </is>
       </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -10134,6 +10399,11 @@
           <t>J255283</t>
         </is>
       </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -10155,6 +10425,11 @@
           <t>J255286</t>
         </is>
       </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -10162,6 +10437,11 @@
           <t>J255287</t>
         </is>
       </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -10169,6 +10449,11 @@
           <t>J255288</t>
         </is>
       </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -10176,6 +10461,11 @@
           <t>J255289</t>
         </is>
       </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -10183,6 +10473,11 @@
           <t>J255290</t>
         </is>
       </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -10190,6 +10485,11 @@
           <t>J255291</t>
         </is>
       </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -10197,6 +10497,11 @@
           <t>J255292</t>
         </is>
       </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -10204,6 +10509,11 @@
           <t>J255294</t>
         </is>
       </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -10211,6 +10521,11 @@
           <t>J255295</t>
         </is>
       </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -10218,6 +10533,11 @@
           <t>J255296</t>
         </is>
       </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -10225,6 +10545,11 @@
           <t>J255297</t>
         </is>
       </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -10232,6 +10557,11 @@
           <t>J255298</t>
         </is>
       </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -10239,6 +10569,11 @@
           <t>J255299</t>
         </is>
       </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -10246,6 +10581,11 @@
           <t>J255300</t>
         </is>
       </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -10253,6 +10593,11 @@
           <t>J255302</t>
         </is>
       </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -10267,6 +10612,11 @@
           <t>J255304</t>
         </is>
       </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -10274,6 +10624,11 @@
           <t>J255305</t>
         </is>
       </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -10281,6 +10636,11 @@
           <t>J255306</t>
         </is>
       </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -10288,6 +10648,11 @@
           <t>J255307</t>
         </is>
       </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -10295,6 +10660,11 @@
           <t>J255308</t>
         </is>
       </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -10309,6 +10679,11 @@
           <t>J255310</t>
         </is>
       </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -10316,6 +10691,11 @@
           <t>J255312</t>
         </is>
       </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -10323,6 +10703,11 @@
           <t>J255314</t>
         </is>
       </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -10330,6 +10715,11 @@
           <t>J255315</t>
         </is>
       </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -10344,6 +10734,11 @@
           <t>J255318</t>
         </is>
       </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -10351,6 +10746,11 @@
           <t>J255319</t>
         </is>
       </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -10358,6 +10758,11 @@
           <t>J255320</t>
         </is>
       </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -10365,6 +10770,11 @@
           <t>J255321</t>
         </is>
       </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -10372,6 +10782,11 @@
           <t>J255322</t>
         </is>
       </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -10379,6 +10794,11 @@
           <t>J255323</t>
         </is>
       </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -10386,6 +10806,11 @@
           <t>J255324</t>
         </is>
       </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -10393,6 +10818,11 @@
           <t>J255325</t>
         </is>
       </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -10400,6 +10830,11 @@
           <t>J255326</t>
         </is>
       </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -10407,6 +10842,11 @@
           <t>J255327</t>
         </is>
       </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -10414,6 +10854,11 @@
           <t>J255328</t>
         </is>
       </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -10421,6 +10866,11 @@
           <t>J255329</t>
         </is>
       </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -10428,6 +10878,11 @@
           <t>J255331</t>
         </is>
       </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -10435,6 +10890,11 @@
           <t>J255332</t>
         </is>
       </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -10456,6 +10916,11 @@
           <t>J255335</t>
         </is>
       </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -10463,6 +10928,11 @@
           <t>J255336</t>
         </is>
       </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -10477,6 +10947,11 @@
           <t>J255338</t>
         </is>
       </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -10484,6 +10959,11 @@
           <t>J255339</t>
         </is>
       </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -10491,6 +10971,11 @@
           <t>J255340</t>
         </is>
       </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -10505,6 +10990,11 @@
           <t>J255342</t>
         </is>
       </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -10512,6 +11002,11 @@
           <t>J255343</t>
         </is>
       </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -10519,6 +11014,11 @@
           <t>J255345</t>
         </is>
       </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -10526,6 +11026,11 @@
           <t>J255347</t>
         </is>
       </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -10533,6 +11038,11 @@
           <t>J255348</t>
         </is>
       </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -10552,6 +11062,11 @@
           <t>J255350</t>
         </is>
       </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -10571,6 +11086,11 @@
           <t>J255352</t>
         </is>
       </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -10590,6 +11110,11 @@
           <t>J255354</t>
         </is>
       </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -10681,6 +11206,11 @@
           <t>J255362</t>
         </is>
       </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -10700,6 +11230,11 @@
           <t>J255364</t>
         </is>
       </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
@@ -10719,6 +11254,11 @@
           <t>J255366</t>
         </is>
       </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
@@ -10750,6 +11290,11 @@
           <t>J255369</t>
         </is>
       </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -10757,6 +11302,11 @@
           <t>J255370</t>
         </is>
       </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -10807,6 +11357,11 @@
           <t>J255377</t>
         </is>
       </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
@@ -10826,6 +11381,11 @@
           <t>J255379</t>
         </is>
       </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -10924,6 +11484,11 @@
           <t>J261001</t>
         </is>
       </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -10955,6 +11520,11 @@
           <t>J261004</t>
         </is>
       </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -11272,6 +11842,11 @@
           <t>J265006</t>
         </is>
       </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -11752,6 +12327,11 @@
           <t>J265058</t>
         </is>
       </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -11828,6 +12408,11 @@
           <t>J265066</t>
         </is>
       </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -11835,6 +12420,11 @@
           <t>J265067</t>
         </is>
       </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -11854,6 +12444,11 @@
           <t>J265069</t>
         </is>
       </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -11909,6 +12504,11 @@
           <t>J265074</t>
         </is>
       </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -11916,6 +12516,11 @@
           <t>J265075</t>
         </is>
       </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
@@ -12494,6 +13099,11 @@
           <t>JOTE063</t>
         </is>
       </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -13325,6 +13935,11 @@
           <t>JX38001</t>
         </is>
       </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -13332,6 +13947,11 @@
           <t>JX38002</t>
         </is>
       </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
@@ -13339,6 +13959,11 @@
           <t>JX38003</t>
         </is>
       </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -13346,6 +13971,11 @@
           <t>JX38004</t>
         </is>
       </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
@@ -13367,6 +13997,11 @@
           <t>JX38007</t>
         </is>
       </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
@@ -13400,6 +14035,11 @@
           <t>JX38012</t>
         </is>
       </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
@@ -13442,6 +14082,11 @@
           <t>KSM3008</t>
         </is>
       </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
@@ -13449,6 +14094,11 @@
           <t>KSM3010</t>
         </is>
       </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
@@ -13456,6 +14106,11 @@
           <t>KSM3013</t>
         </is>
       </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
@@ -13463,6 +14118,11 @@
           <t>KSM3015</t>
         </is>
       </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
@@ -13470,6 +14130,11 @@
           <t>KSM3016</t>
         </is>
       </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
@@ -13477,6 +14142,11 @@
           <t>KSM3018</t>
         </is>
       </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -13484,6 +14154,11 @@
           <t>KSM3020</t>
         </is>
       </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -13491,6 +14166,11 @@
           <t>LEAD005</t>
         </is>
       </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -13498,6 +14178,11 @@
           <t>LEAD007</t>
         </is>
       </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
@@ -13519,6 +14204,11 @@
           <t>LNXB004</t>
         </is>
       </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -13526,6 +14216,11 @@
           <t>LNXB005</t>
         </is>
       </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -13533,6 +14228,11 @@
           <t>LNXB006</t>
         </is>
       </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -13540,6 +14240,11 @@
           <t>LNXB007</t>
         </is>
       </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -13547,6 +14252,11 @@
           <t>LNXB008</t>
         </is>
       </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -13680,6 +14390,11 @@
           <t>LNXC020</t>
         </is>
       </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
@@ -13730,6 +14445,11 @@
           <t>LNXC025</t>
         </is>
       </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -13737,6 +14457,11 @@
           <t>LNXC026</t>
         </is>
       </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -13744,6 +14469,11 @@
           <t>LNXC027</t>
         </is>
       </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -13751,6 +14481,11 @@
           <t>LNXC028</t>
         </is>
       </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -13777,6 +14512,11 @@
           <t>LNXC031</t>
         </is>
       </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
@@ -13784,6 +14524,11 @@
           <t>LNXC032</t>
         </is>
       </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
@@ -13791,6 +14536,11 @@
           <t>LNXC033</t>
         </is>
       </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -13798,6 +14548,11 @@
           <t>LNXC034</t>
         </is>
       </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -13805,6 +14560,11 @@
           <t>LNXC035</t>
         </is>
       </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -13819,6 +14579,11 @@
           <t>LNXC037</t>
         </is>
       </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -13826,6 +14591,11 @@
           <t>LNXC038</t>
         </is>
       </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -13840,6 +14610,11 @@
           <t>LNXC040</t>
         </is>
       </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -13847,6 +14622,11 @@
           <t>LNXC041</t>
         </is>
       </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -14113,6 +14893,11 @@
           <t>LNXD046</t>
         </is>
       </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
@@ -14120,6 +14905,11 @@
           <t>LNXD047</t>
         </is>
       </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
@@ -14148,6 +14938,11 @@
           <t>LNXD051</t>
         </is>
       </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
@@ -14155,6 +14950,11 @@
           <t>LNXD052</t>
         </is>
       </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
@@ -14162,6 +14962,11 @@
           <t>LNXD053</t>
         </is>
       </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -14169,6 +14974,11 @@
           <t>LNXD055</t>
         </is>
       </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -14176,6 +14986,11 @@
           <t>LNXD056</t>
         </is>
       </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
@@ -14183,6 +14998,11 @@
           <t>LNXD057</t>
         </is>
       </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -14190,6 +15010,11 @@
           <t>LNXD058</t>
         </is>
       </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
@@ -14197,6 +15022,11 @@
           <t>LNXD059</t>
         </is>
       </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
@@ -14204,6 +15034,11 @@
           <t>LNXN001</t>
         </is>
       </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -14211,6 +15046,11 @@
           <t>LNXN002</t>
         </is>
       </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
@@ -14218,6 +15058,11 @@
           <t>LNXN003</t>
         </is>
       </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
@@ -14225,6 +15070,11 @@
           <t>LNXN004</t>
         </is>
       </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
@@ -14232,6 +15082,11 @@
           <t>LNXN005</t>
         </is>
       </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -14239,6 +15094,11 @@
           <t>LNXN006</t>
         </is>
       </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
@@ -14246,6 +15106,11 @@
           <t>LNXN007</t>
         </is>
       </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
@@ -14253,6 +15118,11 @@
           <t>LNXN008</t>
         </is>
       </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
@@ -14260,6 +15130,11 @@
           <t>LNXN009</t>
         </is>
       </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
@@ -14267,6 +15142,11 @@
           <t>LNXN010</t>
         </is>
       </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
@@ -14274,6 +15154,11 @@
           <t>LNXN011</t>
         </is>
       </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
@@ -14281,6 +15166,11 @@
           <t>LNXN012</t>
         </is>
       </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
@@ -14288,6 +15178,11 @@
           <t>LNXN013</t>
         </is>
       </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
@@ -14295,6 +15190,11 @@
           <t>LNXN014</t>
         </is>
       </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
@@ -14302,6 +15202,11 @@
           <t>LNXN015</t>
         </is>
       </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
@@ -14309,6 +15214,11 @@
           <t>LNXN016</t>
         </is>
       </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -14316,6 +15226,11 @@
           <t>LNXN018</t>
         </is>
       </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
@@ -14323,6 +15238,11 @@
           <t>LNXN019</t>
         </is>
       </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
@@ -14330,6 +15250,11 @@
           <t>LNXN021</t>
         </is>
       </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
@@ -14337,6 +15262,11 @@
           <t>LNXN023</t>
         </is>
       </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
@@ -14344,6 +15274,11 @@
           <t>LNXN024</t>
         </is>
       </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
@@ -14351,6 +15286,11 @@
           <t>LNXN025</t>
         </is>
       </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
@@ -14358,6 +15298,11 @@
           <t>LNXN027</t>
         </is>
       </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
@@ -14365,6 +15310,11 @@
           <t>LNXN029</t>
         </is>
       </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
@@ -14372,6 +15322,11 @@
           <t>LNXN030</t>
         </is>
       </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -14379,6 +15334,11 @@
           <t>LNXN031</t>
         </is>
       </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
@@ -14386,6 +15346,11 @@
           <t>LNXN032</t>
         </is>
       </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -14393,6 +15358,11 @@
           <t>LNXN033</t>
         </is>
       </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
@@ -14400,6 +15370,11 @@
           <t>LNXN034</t>
         </is>
       </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
@@ -14407,6 +15382,11 @@
           <t>LNXN035</t>
         </is>
       </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
@@ -14414,6 +15394,11 @@
           <t>LNXN036</t>
         </is>
       </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
@@ -14421,6 +15406,11 @@
           <t>LNXN037</t>
         </is>
       </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
@@ -14428,6 +15418,11 @@
           <t>LNXN038</t>
         </is>
       </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
@@ -14435,6 +15430,11 @@
           <t>LNXN039</t>
         </is>
       </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -14442,6 +15442,11 @@
           <t>LNXN040</t>
         </is>
       </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
@@ -14449,6 +15454,11 @@
           <t>LNXN041</t>
         </is>
       </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
@@ -14456,6 +15466,11 @@
           <t>LNXN042</t>
         </is>
       </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
@@ -14463,6 +15478,11 @@
           <t>LNXN043</t>
         </is>
       </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
@@ -17666,6 +18686,11 @@
           <t>LNXN418</t>
         </is>
       </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
@@ -17757,6 +18782,11 @@
           <t>LNXN426</t>
         </is>
       </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
@@ -17764,6 +18794,11 @@
           <t>LNXN427</t>
         </is>
       </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
@@ -17831,6 +18866,11 @@
           <t>LNXN434</t>
         </is>
       </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
@@ -17838,6 +18878,11 @@
           <t>LNXN435</t>
         </is>
       </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
@@ -17857,6 +18902,11 @@
           <t>LNXN437</t>
         </is>
       </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
@@ -17876,6 +18926,11 @@
           <t>LNXO001</t>
         </is>
       </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
@@ -18353,6 +19408,11 @@
           <t>LX40057</t>
         </is>
       </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
@@ -18360,6 +19420,11 @@
           <t>LX40058</t>
         </is>
       </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
@@ -18367,6 +19432,11 @@
           <t>LX40059</t>
         </is>
       </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
@@ -18374,6 +19444,11 @@
           <t>LX40060</t>
         </is>
       </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
@@ -18381,6 +19456,11 @@
           <t>LX40061</t>
         </is>
       </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
@@ -18395,6 +19475,11 @@
           <t>LX40063</t>
         </is>
       </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
@@ -18402,6 +19487,11 @@
           <t>LX40064</t>
         </is>
       </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
@@ -18409,6 +19499,11 @@
           <t>LX40065</t>
         </is>
       </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
@@ -18416,6 +19511,11 @@
           <t>LX40066</t>
         </is>
       </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
@@ -18423,6 +19523,11 @@
           <t>LX40067</t>
         </is>
       </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
@@ -18430,6 +19535,11 @@
           <t>LX40068</t>
         </is>
       </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
@@ -18437,6 +19547,11 @@
           <t>LX40069</t>
         </is>
       </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
@@ -18444,6 +19559,11 @@
           <t>LX40070</t>
         </is>
       </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
@@ -18451,6 +19571,11 @@
           <t>LX40071</t>
         </is>
       </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
@@ -18458,6 +19583,11 @@
           <t>LX40072</t>
         </is>
       </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
@@ -18465,6 +19595,11 @@
           <t>LX40073</t>
         </is>
       </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
@@ -18472,6 +19607,11 @@
           <t>LX40074</t>
         </is>
       </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1846">
       <c r="A1846" t="inlineStr">
@@ -18479,6 +19619,11 @@
           <t>LX40075</t>
         </is>
       </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
@@ -18486,6 +19631,11 @@
           <t>LX40076</t>
         </is>
       </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
@@ -18493,6 +19643,11 @@
           <t>LX40077</t>
         </is>
       </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
@@ -18500,6 +19655,11 @@
           <t>LX40078</t>
         </is>
       </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
@@ -18507,6 +19667,11 @@
           <t>LX40079</t>
         </is>
       </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1851">
       <c r="A1851" t="inlineStr">
@@ -18514,6 +19679,11 @@
           <t>LX40080</t>
         </is>
       </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1852">
       <c r="A1852" t="inlineStr">
@@ -18521,6 +19691,11 @@
           <t>LX40081</t>
         </is>
       </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1853">
       <c r="A1853" t="inlineStr">
@@ -18528,6 +19703,11 @@
           <t>LX40082</t>
         </is>
       </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1854">
       <c r="A1854" t="inlineStr">
@@ -18535,6 +19715,11 @@
           <t>LX40083</t>
         </is>
       </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
@@ -18542,6 +19727,11 @@
           <t>LX40084</t>
         </is>
       </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1856">
       <c r="A1856" t="inlineStr">
@@ -18549,6 +19739,11 @@
           <t>LX40085</t>
         </is>
       </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1857">
       <c r="A1857" t="inlineStr">
@@ -18556,6 +19751,11 @@
           <t>LX40086</t>
         </is>
       </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1858">
       <c r="A1858" t="inlineStr">
@@ -18563,6 +19763,11 @@
           <t>LX40087</t>
         </is>
       </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
@@ -18570,6 +19775,11 @@
           <t>LX40088</t>
         </is>
       </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
@@ -18577,6 +19787,11 @@
           <t>LX40089</t>
         </is>
       </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1861">
       <c r="A1861" t="inlineStr">
@@ -18584,6 +19799,11 @@
           <t>LX40090</t>
         </is>
       </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1862">
       <c r="A1862" t="inlineStr">
@@ -18591,6 +19811,11 @@
           <t>LX40091</t>
         </is>
       </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1863">
       <c r="A1863" t="inlineStr">
@@ -18598,6 +19823,11 @@
           <t>LX40092</t>
         </is>
       </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1864">
       <c r="A1864" t="inlineStr">
@@ -18605,6 +19835,11 @@
           <t>LX40093</t>
         </is>
       </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
@@ -18612,6 +19847,11 @@
           <t>LX40094</t>
         </is>
       </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
@@ -18619,6 +19859,11 @@
           <t>LX40095</t>
         </is>
       </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1867">
       <c r="A1867" t="inlineStr">
@@ -18626,6 +19871,11 @@
           <t>LX40096</t>
         </is>
       </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
@@ -18633,6 +19883,11 @@
           <t>LX40097</t>
         </is>
       </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
@@ -18640,6 +19895,11 @@
           <t>LX40098</t>
         </is>
       </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1870">
       <c r="A1870" t="inlineStr">
@@ -18647,6 +19907,11 @@
           <t>LX40099</t>
         </is>
       </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1871">
       <c r="A1871" t="inlineStr">
@@ -18654,6 +19919,11 @@
           <t>LX40100</t>
         </is>
       </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1872">
       <c r="A1872" t="inlineStr">
@@ -18661,6 +19931,11 @@
           <t>LX40101</t>
         </is>
       </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1873">
       <c r="A1873" t="inlineStr">
@@ -18668,6 +19943,11 @@
           <t>LX40102</t>
         </is>
       </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1874">
       <c r="A1874" t="inlineStr">
@@ -18675,6 +19955,11 @@
           <t>LX40103</t>
         </is>
       </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1875">
       <c r="A1875" t="inlineStr">
@@ -18682,6 +19967,11 @@
           <t>LX40104</t>
         </is>
       </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1876">
       <c r="A1876" t="inlineStr">
@@ -18689,6 +19979,11 @@
           <t>LX40105</t>
         </is>
       </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1877">
       <c r="A1877" t="inlineStr">
@@ -18696,6 +19991,11 @@
           <t>LX40106</t>
         </is>
       </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1878">
       <c r="A1878" t="inlineStr">
@@ -18703,6 +20003,11 @@
           <t>LX40107</t>
         </is>
       </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1879">
       <c r="A1879" t="inlineStr">
@@ -18710,6 +20015,11 @@
           <t>LX40108</t>
         </is>
       </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1880">
       <c r="A1880" t="inlineStr">
@@ -18717,6 +20027,11 @@
           <t>LX40109</t>
         </is>
       </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1881">
       <c r="A1881" t="inlineStr">
@@ -18724,6 +20039,11 @@
           <t>LX40111</t>
         </is>
       </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1882">
       <c r="A1882" t="inlineStr">
@@ -18731,6 +20051,11 @@
           <t>LX40112</t>
         </is>
       </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1883">
       <c r="A1883" t="inlineStr">
@@ -18738,6 +20063,11 @@
           <t>LX40113</t>
         </is>
       </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1884">
       <c r="A1884" t="inlineStr">
@@ -18745,6 +20075,11 @@
           <t>LX40114</t>
         </is>
       </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1885">
       <c r="A1885" t="inlineStr">
@@ -18752,6 +20087,11 @@
           <t>LX40115</t>
         </is>
       </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1886">
       <c r="A1886" t="inlineStr">
@@ -18759,6 +20099,11 @@
           <t>LX40116</t>
         </is>
       </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1887">
       <c r="A1887" t="inlineStr">
@@ -18773,6 +20118,11 @@
           <t>LX40118</t>
         </is>
       </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1889">
       <c r="A1889" t="inlineStr">
@@ -18780,6 +20130,11 @@
           <t>LX40119</t>
         </is>
       </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1890">
       <c r="A1890" t="inlineStr">
@@ -18794,6 +20149,11 @@
           <t>LX40121</t>
         </is>
       </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1892">
       <c r="A1892" t="inlineStr">
@@ -18801,6 +20161,11 @@
           <t>LX40122</t>
         </is>
       </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1893">
       <c r="A1893" t="inlineStr">
@@ -18808,6 +20173,11 @@
           <t>LX40123</t>
         </is>
       </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1894">
       <c r="A1894" t="inlineStr">
@@ -18815,6 +20185,11 @@
           <t>LX40124</t>
         </is>
       </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1895">
       <c r="A1895" t="inlineStr">
@@ -18822,6 +20197,11 @@
           <t>LX40126</t>
         </is>
       </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1896">
       <c r="A1896" t="inlineStr">
@@ -18829,6 +20209,11 @@
           <t>LX40127</t>
         </is>
       </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1897">
       <c r="A1897" t="inlineStr">
@@ -18836,6 +20221,11 @@
           <t>LX40128</t>
         </is>
       </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1898">
       <c r="A1898" t="inlineStr">
@@ -18843,6 +20233,11 @@
           <t>LX60001</t>
         </is>
       </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1899">
       <c r="A1899" t="inlineStr">
@@ -18850,6 +20245,11 @@
           <t>LX60002</t>
         </is>
       </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1900">
       <c r="A1900" t="inlineStr">
@@ -18857,6 +20257,11 @@
           <t>LX60003</t>
         </is>
       </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1901">
       <c r="A1901" t="inlineStr">
@@ -18864,6 +20269,11 @@
           <t>LX60004</t>
         </is>
       </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1902">
       <c r="A1902" t="inlineStr">
@@ -18871,6 +20281,11 @@
           <t>LX60005</t>
         </is>
       </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1903">
       <c r="A1903" t="inlineStr">
@@ -18878,6 +20293,11 @@
           <t>LX60006</t>
         </is>
       </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1904">
       <c r="A1904" t="inlineStr">
@@ -18885,6 +20305,11 @@
           <t>LX60007</t>
         </is>
       </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1905">
       <c r="A1905" t="inlineStr">
@@ -18892,6 +20317,11 @@
           <t>LX60008</t>
         </is>
       </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1906">
       <c r="A1906" t="inlineStr">
@@ -19719,6 +21149,11 @@
           <t>M115084</t>
         </is>
       </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="1982">
       <c r="A1982" t="inlineStr">
@@ -20247,6 +21682,11 @@
           <t>M115135</t>
         </is>
       </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2031">
       <c r="A2031" t="inlineStr">
@@ -20724,6 +22164,11 @@
           <t>M115178</t>
         </is>
       </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2072">
       <c r="A2072" t="inlineStr">
@@ -20731,6 +22176,11 @@
           <t>M115179</t>
         </is>
       </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2073">
       <c r="A2073" t="inlineStr">
@@ -20738,6 +22188,11 @@
           <t>M115180</t>
         </is>
       </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2074">
       <c r="A2074" t="inlineStr">
@@ -20793,6 +22248,11 @@
           <t>M115186</t>
         </is>
       </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2079">
       <c r="A2079" t="inlineStr">
@@ -20824,6 +22284,11 @@
           <t>M115190</t>
         </is>
       </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2082">
       <c r="A2082" t="inlineStr">
@@ -20831,6 +22296,11 @@
           <t>M115191</t>
         </is>
       </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2083">
       <c r="A2083" t="inlineStr">
@@ -20838,6 +22308,11 @@
           <t>M115192</t>
         </is>
       </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2084">
       <c r="A2084" t="inlineStr">
@@ -20845,6 +22320,11 @@
           <t>M115193</t>
         </is>
       </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2085">
       <c r="A2085" t="inlineStr">
@@ -20871,6 +22351,11 @@
           <t>M115198</t>
         </is>
       </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2088">
       <c r="A2088" t="inlineStr">
@@ -22000,6 +23485,11 @@
           <t>MGUT073</t>
         </is>
       </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2185">
       <c r="A2185" t="inlineStr">
@@ -22007,6 +23497,11 @@
           <t>MGUT075</t>
         </is>
       </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2186">
       <c r="A2186" t="inlineStr">
@@ -22014,6 +23509,11 @@
           <t>MGUT076</t>
         </is>
       </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2187">
       <c r="A2187" t="inlineStr">
@@ -22057,6 +23557,11 @@
           <t>MGUT080</t>
         </is>
       </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2191">
       <c r="A2191" t="inlineStr">
@@ -22541,6 +24046,11 @@
           <t>T2D2018</t>
         </is>
       </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2233">
       <c r="A2233" t="inlineStr">
@@ -22694,6 +24204,11 @@
           <t>T2D3014</t>
         </is>
       </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2247">
       <c r="A2247" t="inlineStr">
@@ -22902,6 +24417,11 @@
           <t>T2D6006</t>
         </is>
       </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2266">
       <c r="A2266" t="inlineStr">
@@ -22909,6 +24429,11 @@
           <t>T2D6007</t>
         </is>
       </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2267">
       <c r="A2267" t="inlineStr">
@@ -22916,6 +24441,11 @@
           <t>T2D6008</t>
         </is>
       </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
@@ -23405,6 +24935,11 @@
           <t>T314030</t>
         </is>
       </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>scaricato</t>
+        </is>
+      </c>
     </row>
     <row r="2310">
       <c r="A2310" t="inlineStr">
@@ -23441,6 +24976,11 @@
       <c r="A2313" t="inlineStr">
         <is>
           <t>T35P004</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>scaricato</t>
         </is>
       </c>
     </row>
